--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week07_12Oct.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week07_12Oct.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I12" s="56" t="inlineStr">
         <is>
-          <t>TA confirms allergy status with the office BEFORE the bag is packed — safeguarding step, not a formality. Teacher runs the iodine demo once, slowly, with LAUNCH's tile. LOOP [Feedback Policy]: Voice = sort/build the plate/point [VF, ?] → Audience: name one group and its job; [R] once received → EVIDENCE: balanced-plate photo, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+          <t>TA confirms allergy status with the office BEFORE the bag is packed — safeguarding step, not a formality. Teacher runs the iodine demo once, slowly, with LAUNCH's tile. LOOP [Feedback Policy]: Voice = sort/build the plate/point [VF, ?] → Audience: name one group and its job; [R] once received → EVIDENCE: balanced-plate photo, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
         </is>
       </c>
       <c r="J12" s="56" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="I13" s="58" t="inlineStr">
         <is>
-          <t>TA rehearses each pupil's part and films the pitch.  LOOP [Feedback Policy]: Voice = choose/plan/pitch [VF] → Audience: name each contribution back; [R] once the permission lands → EVIDENCE: board + clip, same day [E: BV/community — daily EFL; banks AQA UAS].</t>
+          <t>TA rehearses each pupil's part and films the pitch.  LOOP [Feedback Policy]: Voice = choose/plan/pitch [VF] → Audience: name each contribution back; [R] once the permission lands → EVIDENCE: board + clip, same day [E: BV/community — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J13" s="58" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="I14" s="56" t="inlineStr">
         <is>
-          <t>TA anchors the quiet corner and records the lines.  LOOP [Feedback Policy]: Voice = make/say the line [VF] → Audience: listen fully, receive it simply, then [R] → EVIDENCE: cascade + lines, same day [E: SMSC — daily EFL].</t>
+          <t>TA anchors the quiet corner and records the lines.  LOOP [Feedback Policy]: Voice = make/say the line [VF] → Audience: listen fully, receive it simply, then [R] → EVIDENCE: cascade + lines, same day [E: SMSC — daily evidence platform].</t>
         </is>
       </c>
       <c r="J14" s="56" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="I15" s="56" t="inlineStr">
         <is>
-          <t>TA runs the recording corner and captures the thumbs-why.  LOOP [Feedback Policy]: Voice = tell/record + thumbs why [VF, ?] → Audience: listen to the whole story before tagging, name the shape back, then [R] → EVIDENCE: recording banked, same day [E: humanities/oracy — daily EFL; banks AQA UAS].</t>
+          <t>TA runs the recording corner and captures the thumbs-why.  LOOP [Feedback Policy]: Voice = tell/record + thumbs why [VF, ?] → Audience: listen to the whole story before tagging, name the shape back, then [R] → EVIDENCE: recording banked, same day [E: humanities/oracy — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr">
